--- a/recommendation_forms/047_player_coach_recommendation_form--recommendation_forms.xlsx
+++ b/recommendation_forms/047_player_coach_recommendation_form--recommendation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'goalkeeper'}</t>
+          <t>goalkeeper</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Goalkeeper'}</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'defender'}</t>
+          <t>defender</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Defender'}</t>
+          <t>Defender</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'midfielder'}</t>
+          <t>midfielder</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Midfielder'}</t>
+          <t>Midfielder</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'forward'}</t>
+          <t>forward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Forward'}</t>
+          <t>Forward</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'head_coach'}</t>
+          <t>head_coach</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Head Coach'}</t>
+          <t>Head Coach</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'assistant_coach'}</t>
+          <t>assistant_coach</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Assistant Coach'}</t>
+          <t>Assistant Coach</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team_a'}</t>
+          <t>team_a</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team A'}</t>
+          <t>Team A</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_b'}</t>
+          <t>team_b</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team B'}</t>
+          <t>Team B</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'team_c'}</t>
+          <t>team_c</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Team C'}</t>
+          <t>Team C</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'team_d'}</t>
+          <t>team_d</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Team D'}</t>
+          <t>Team D</t>
         </is>
       </c>
     </row>
